--- a/jeaf-generator-test-deprecation-report/src-gen/main/resources/Breaking_Changes.xlsx
+++ b/jeaf-generator-test-deprecation-report/src-gen/main/resources/Breaking_Changes.xlsx
@@ -251,7 +251,7 @@
     <t>7.0</t>
   </si>
   <si>
-    <t>2026-09-13</t>
+    <t>2026-12-24</t>
   </si>
   <si>
     <t>upcomingMandatoryProperty</t>
@@ -272,7 +272,7 @@
     <t>8.0</t>
   </si>
   <si>
-    <t>2026-10-20</t>
+    <t>2027-05-01</t>
   </si>
 </sst>
 </file>

--- a/jeaf-generator-test-deprecation-report/src-gen/main/resources/Breaking_Changes.xlsx
+++ b/jeaf-generator-test-deprecation-report/src-gen/main/resources/Breaking_Changes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tillmann.schall/Projects/JEAF/jeaf-generator/jeaf-generator/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A25722-840F-934A-ACD6-3B8034AE6408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F7BBC5-68D7-064A-BEE6-325E2F2001A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4640" yWindow="620" windowWidth="29960" windowHeight="28140" xr2:uid="{441949ED-3404-8548-92CD-A40A7EA6D1DC}"/>
   </bookViews>
@@ -59,7 +59,7 @@
     <t>Active with</t>
   </si>
   <si>
-    <t>Activation Date</t>
+    <t>Go Live  Date</t>
   </si>
   <si>
     <t>ServiceWithDeprecations.createSomething(...)</t>
@@ -355,25 +355,25 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -405,12 +405,6 @@
       <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -423,11 +417,17 @@
       </border>
     </dxf>
     <dxf>
+      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border outline="0">
         <bottom style="thin">
           <color theme="4"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -443,16 +443,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}" name="Table1" displayName="Table1" ref="A1:G1048576" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4" headerRowBorderDxfId="10" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}" name="Table1" displayName="Table1" ref="A1:G1048576" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
   <autoFilter ref="A1:G1048576" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{A4DDCCBB-E133-DF45-8389-C4AD19D8AEB7}" name="Element" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{439690A4-77A7-D848-A33C-19AF8EF0CF49}" name="Package" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{BC971382-1AD8-4C4D-972D-DF92F8F0260A}" name="Details" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{A4DDCCBB-E133-DF45-8389-C4AD19D8AEB7}" name="Element" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{439690A4-77A7-D848-A33C-19AF8EF0CF49}" name="Package" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{BC971382-1AD8-4C4D-972D-DF92F8F0260A}" name="Details" dataDxfId="4"/>
     <tableColumn id="5" xr3:uid="{1DDDD3D3-BC66-DB4E-A899-65EA0DA59605}" name="Description" dataDxfId="3"/>
     <tableColumn id="6" xr3:uid="{122F67FD-2569-C44A-A432-EAFF5935108B}" name="Since" dataDxfId="2"/>
     <tableColumn id="7" xr3:uid="{4B86B03A-67C7-E347-8943-3AB848258236}" name="Active with" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{E69C5988-012E-2C46-A6D4-42119249395E}" name="Activation Date" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{E69C5988-012E-2C46-A6D4-42119249395E}" name="Go Live  Date" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>

--- a/jeaf-generator-test-deprecation-report/src-gen/main/resources/Breaking_Changes.xlsx
+++ b/jeaf-generator-test-deprecation-report/src-gen/main/resources/Breaking_Changes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tillmann.schall/Projects/JEAF/jeaf-generator/jeaf-generator/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F7BBC5-68D7-064A-BEE6-325E2F2001A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80C823A2-D35B-9242-AF25-689A1C616038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4640" yWindow="620" windowWidth="29960" windowHeight="28140" xr2:uid="{441949ED-3404-8548-92CD-A40A7EA6D1DC}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="81">
   <si>
     <t>Package</t>
   </si>
@@ -62,6 +62,9 @@
     <t>Go Live  Date</t>
   </si>
   <si>
+    <t>End of Compatibility Phase</t>
+  </si>
+  <si>
     <t>ServiceWithDeprecations.createSomething(...)</t>
   </si>
   <si>
@@ -254,6 +257,9 @@
     <t>2026-12-24</t>
   </si>
   <si>
+    <t>2026-09-13</t>
+  </si>
+  <si>
     <t>upcomingMandatoryProperty</t>
   </si>
   <si>
@@ -273,6 +279,9 @@
   </si>
   <si>
     <t>2027-05-01</t>
+  </si>
+  <si>
+    <t>2026-10-20</t>
   </si>
 </sst>
 </file>
@@ -341,7 +350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -376,11 +385,17 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="12">
+    <dxf>
+      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -443,16 +458,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}" name="Table1" displayName="Table1" ref="A1:G1048576" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
-  <autoFilter ref="A1:G1048576" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{A4DDCCBB-E133-DF45-8389-C4AD19D8AEB7}" name="Element" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{439690A4-77A7-D848-A33C-19AF8EF0CF49}" name="Package" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{BC971382-1AD8-4C4D-972D-DF92F8F0260A}" name="Details" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{1DDDD3D3-BC66-DB4E-A899-65EA0DA59605}" name="Description" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{122F67FD-2569-C44A-A432-EAFF5935108B}" name="Since" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{4B86B03A-67C7-E347-8943-3AB848258236}" name="Active with" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{E69C5988-012E-2C46-A6D4-42119249395E}" name="Go Live  Date" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}" name="Table1" displayName="Table1" ref="A1:H1048576" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8">
+  <autoFilter ref="A1:H1048576" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{A4DDCCBB-E133-DF45-8389-C4AD19D8AEB7}" name="Element" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{439690A4-77A7-D848-A33C-19AF8EF0CF49}" name="Package" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{BC971382-1AD8-4C4D-972D-DF92F8F0260A}" name="Details" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{1DDDD3D3-BC66-DB4E-A899-65EA0DA59605}" name="Description" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{122F67FD-2569-C44A-A432-EAFF5935108B}" name="Since" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{4B86B03A-67C7-E347-8943-3AB848258236}" name="Active with" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{E69C5988-012E-2C46-A6D4-42119249395E}" name="Go Live  Date" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{BA3D9D58-4D63-3545-A4C7-20399432C0A1}" name="End of Compatibility Phase" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -775,7 +791,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1136C3-A1B3-DD42-A00A-DCFCD8D149EA}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="9" width="31.5"/>
@@ -784,9 +800,10 @@
     <col min="4" max="4" customWidth="true" style="9" width="60.33203125"/>
     <col min="5" max="5" customWidth="true" style="10" width="31.5"/>
     <col min="6" max="7" customWidth="true" style="11" width="31.5"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="9" width="26.0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -808,419 +825,476 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="12" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s" s="9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s" s="9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s" s="9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H2" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="9">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s" s="9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s" s="9">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s" s="11">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H3" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s" s="9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s" s="9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s" s="11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H4" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s" s="9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s" s="9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s" s="11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H5" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s" s="9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s" s="9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s" s="11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G6" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H6" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s" s="9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s" s="9">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s" s="11">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G7" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H7" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s" s="9">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s" s="9">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s" s="11">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G8" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H8" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="9">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s" s="9">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s" s="9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s" s="11">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G9" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H9" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="9">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s" s="9">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s" s="9">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s" s="11">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G10" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H10" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="9">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s" s="9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s" s="9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s" s="11">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G11" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H11" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="9">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12" t="s" s="9">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s" s="9">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s" s="9">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E12" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F12" t="s" s="11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G12" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H12" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="9">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s" s="9">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s" s="9">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s" s="9">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s" s="11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G13" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H13" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="9">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s" s="9">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C14" t="s" s="9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s" s="9">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s" s="10">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F14" t="s" s="11">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G14" t="s" s="11">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="H14" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="9">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B15" t="s" s="9">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s" s="9">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s" s="9">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s" s="10">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F15" t="s" s="11">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G15" t="s" s="11">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="H15" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="9">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s" s="9">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s" s="9">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s" s="9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F16" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H16" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="9">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s" s="9">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s" s="9">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s" s="9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F17" t="s" s="11">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G17" t="s" s="11">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="H17" t="s" s="9">
+        <v>72</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="9">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B18" t="s" s="9">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s" s="9">
+        <v>73</v>
+      </c>
+      <c r="D18" t="s" s="9">
+        <v>74</v>
+      </c>
+      <c r="E18" t="s" s="10">
+        <v>12</v>
+      </c>
+      <c r="F18" t="s" s="11">
+        <v>70</v>
+      </c>
+      <c r="G18" t="s" s="11">
         <v>71</v>
       </c>
-      <c r="D18" t="s" s="9">
+      <c r="H18" t="s" s="9">
         <v>72</v>
-      </c>
-      <c r="E18" t="s" s="10">
-        <v>11</v>
-      </c>
-      <c r="F18" t="s" s="11">
-        <v>69</v>
-      </c>
-      <c r="G18" t="s" s="11">
-        <v>70</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="9">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s" s="9">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s" s="9">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s" s="9">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E19" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F19" t="s" s="11">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G19" t="s" s="11">
-        <v>77</v>
+        <v>79</v>
+      </c>
+      <c r="H19" t="s" s="9">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/jeaf-generator-test-deprecation-report/src-gen/main/resources/Breaking_Changes.xlsx
+++ b/jeaf-generator-test-deprecation-report/src-gen/main/resources/Breaking_Changes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tillmann.schall/Projects/JEAF/jeaf-generator/jeaf-generator/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80C823A2-D35B-9242-AF25-689A1C616038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21213A85-80EA-254D-BE5D-82FA035F7A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4640" yWindow="620" windowWidth="29960" windowHeight="28140" xr2:uid="{441949ED-3404-8548-92CD-A40A7EA6D1DC}"/>
   </bookViews>
@@ -62,7 +62,7 @@
     <t>Go Live  Date</t>
   </si>
   <si>
-    <t>End of Compatibility Phase</t>
+    <t>End of Compatibility Period</t>
   </si>
   <si>
     <t>ServiceWithDeprecations.createSomething(...)</t>
@@ -468,7 +468,7 @@
     <tableColumn id="6" xr3:uid="{122F67FD-2569-C44A-A432-EAFF5935108B}" name="Since" dataDxfId="3"/>
     <tableColumn id="7" xr3:uid="{4B86B03A-67C7-E347-8943-3AB848258236}" name="Active with" dataDxfId="2"/>
     <tableColumn id="8" xr3:uid="{E69C5988-012E-2C46-A6D4-42119249395E}" name="Go Live  Date" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{BA3D9D58-4D63-3545-A4C7-20399432C0A1}" name="End of Compatibility Phase" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{BA3D9D58-4D63-3545-A4C7-20399432C0A1}" name="End of Compatibility Period" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -800,7 +800,7 @@
     <col min="4" max="4" customWidth="true" style="9" width="60.33203125"/>
     <col min="5" max="5" customWidth="true" style="10" width="31.5"/>
     <col min="6" max="7" customWidth="true" style="11" width="31.5"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="9" width="26.0"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="9" width="26.1640625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">

--- a/jeaf-generator-test-deprecation-report/src-gen/main/resources/Breaking_Changes.xlsx
+++ b/jeaf-generator-test-deprecation-report/src-gen/main/resources/Breaking_Changes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tillmann.schall/Projects/JEAF/jeaf-generator/jeaf-generator/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A25722-840F-934A-ACD6-3B8034AE6408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21213A85-80EA-254D-BE5D-82FA035F7A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4640" yWindow="620" windowWidth="29960" windowHeight="28140" xr2:uid="{441949ED-3404-8548-92CD-A40A7EA6D1DC}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="81">
   <si>
     <t>Package</t>
   </si>
@@ -59,7 +59,10 @@
     <t>Active with</t>
   </si>
   <si>
-    <t>Activation Date</t>
+    <t>Go Live  Date</t>
+  </si>
+  <si>
+    <t>End of Compatibility Period</t>
   </si>
   <si>
     <t>ServiceWithDeprecations.createSomething(...)</t>
@@ -251,6 +254,9 @@
     <t>7.0</t>
   </si>
   <si>
+    <t>2026-12-24</t>
+  </si>
+  <si>
     <t>2026-09-13</t>
   </si>
   <si>
@@ -270,6 +276,9 @@
   </si>
   <si>
     <t>8.0</t>
+  </si>
+  <si>
+    <t>2027-05-01</t>
   </si>
   <si>
     <t>2026-10-20</t>
@@ -341,7 +350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -355,32 +364,38 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="12">
+    <dxf>
+      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -391,12 +406,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -423,11 +432,17 @@
       </border>
     </dxf>
     <dxf>
+      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border outline="0">
         <bottom style="thin">
           <color theme="4"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -443,16 +458,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}" name="Table1" displayName="Table1" ref="A1:G1048576" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4" headerRowBorderDxfId="10" tableBorderDxfId="9">
-  <autoFilter ref="A1:G1048576" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{A4DDCCBB-E133-DF45-8389-C4AD19D8AEB7}" name="Element" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{439690A4-77A7-D848-A33C-19AF8EF0CF49}" name="Package" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{BC971382-1AD8-4C4D-972D-DF92F8F0260A}" name="Details" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{1DDDD3D3-BC66-DB4E-A899-65EA0DA59605}" name="Description" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{122F67FD-2569-C44A-A432-EAFF5935108B}" name="Since" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{4B86B03A-67C7-E347-8943-3AB848258236}" name="Active with" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{E69C5988-012E-2C46-A6D4-42119249395E}" name="Activation Date" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}" name="Table1" displayName="Table1" ref="A1:H1048576" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8">
+  <autoFilter ref="A1:H1048576" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{A4DDCCBB-E133-DF45-8389-C4AD19D8AEB7}" name="Element" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{439690A4-77A7-D848-A33C-19AF8EF0CF49}" name="Package" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{BC971382-1AD8-4C4D-972D-DF92F8F0260A}" name="Details" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{1DDDD3D3-BC66-DB4E-A899-65EA0DA59605}" name="Description" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{122F67FD-2569-C44A-A432-EAFF5935108B}" name="Since" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{4B86B03A-67C7-E347-8943-3AB848258236}" name="Active with" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{E69C5988-012E-2C46-A6D4-42119249395E}" name="Go Live  Date" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{BA3D9D58-4D63-3545-A4C7-20399432C0A1}" name="End of Compatibility Period" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -775,7 +791,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1136C3-A1B3-DD42-A00A-DCFCD8D149EA}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="9" width="31.5"/>
@@ -784,9 +800,10 @@
     <col min="4" max="4" customWidth="true" style="9" width="60.33203125"/>
     <col min="5" max="5" customWidth="true" style="10" width="31.5"/>
     <col min="6" max="7" customWidth="true" style="11" width="31.5"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="9" width="26.1640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -808,419 +825,476 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="12" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s" s="9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s" s="9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s" s="9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H2" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="9">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s" s="9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s" s="9">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s" s="11">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H3" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s" s="9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s" s="9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s" s="11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H4" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s" s="9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s" s="9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s" s="11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H5" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s" s="9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s" s="9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s" s="11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G6" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H6" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s" s="9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s" s="9">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s" s="11">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G7" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H7" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="9">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s" s="9">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s" s="9">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s" s="11">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G8" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H8" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="9">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s" s="9">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s" s="9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s" s="11">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G9" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H9" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="9">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s" s="9">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s" s="9">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s" s="11">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G10" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H10" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="9">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s" s="9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s" s="9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s" s="11">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G11" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H11" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="9">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12" t="s" s="9">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s" s="9">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s" s="9">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E12" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F12" t="s" s="11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G12" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H12" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="9">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s" s="9">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s" s="9">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s" s="9">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s" s="11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G13" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H13" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="9">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s" s="9">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C14" t="s" s="9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s" s="9">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s" s="10">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F14" t="s" s="11">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G14" t="s" s="11">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="H14" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="9">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B15" t="s" s="9">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s" s="9">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s" s="9">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s" s="10">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F15" t="s" s="11">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G15" t="s" s="11">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="H15" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="9">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s" s="9">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s" s="9">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s" s="9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F16" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16" t="s" s="11">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H16" t="s" s="9">
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="9">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s" s="9">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s" s="9">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s" s="9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F17" t="s" s="11">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G17" t="s" s="11">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="H17" t="s" s="9">
+        <v>72</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="9">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B18" t="s" s="9">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s" s="9">
+        <v>73</v>
+      </c>
+      <c r="D18" t="s" s="9">
+        <v>74</v>
+      </c>
+      <c r="E18" t="s" s="10">
+        <v>12</v>
+      </c>
+      <c r="F18" t="s" s="11">
+        <v>70</v>
+      </c>
+      <c r="G18" t="s" s="11">
         <v>71</v>
       </c>
-      <c r="D18" t="s" s="9">
+      <c r="H18" t="s" s="9">
         <v>72</v>
-      </c>
-      <c r="E18" t="s" s="10">
-        <v>11</v>
-      </c>
-      <c r="F18" t="s" s="11">
-        <v>69</v>
-      </c>
-      <c r="G18" t="s" s="11">
-        <v>70</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="9">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s" s="9">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s" s="9">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s" s="9">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E19" t="s" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F19" t="s" s="11">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G19" t="s" s="11">
-        <v>77</v>
+        <v>79</v>
+      </c>
+      <c r="H19" t="s" s="9">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
